--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-observation-statut.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-observation-statut.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4369" uniqueCount="631">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1082,6 +1082,245 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>Observation.value[x]</t>
   </si>
   <si>
@@ -1141,9 +1380,6 @@
     <t>Qualifier du code</t>
   </si>
   <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t>Observation.value[x].coding.extension:qualifier.id</t>
   </si>
   <si>
@@ -1156,12 +1392,6 @@
     <t>Observation.value[x].coding.extension.extension</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
     <t>Observation.value[x].coding.extension:qualifier.extension:name</t>
   </si>
   <si>
@@ -1186,28 +1416,10 @@
     <t>Observation.value[x].coding.extension.extension.url</t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
     <t>Observation.value[x].coding.extension:qualifier.extension:name.value[x]</t>
   </si>
   <si>
     <t>Observation.value[x].coding.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1219,9 +1431,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
     <t>Observation.value[x].coding.extension:qualifier.extension:value</t>
   </si>
   <si>
@@ -1250,10 +1459,6 @@
   </si>
   <si>
     <t>Observation.value[x].coding.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Observation.value[x].coding.system</t>
@@ -1288,9 +1493,6 @@
   </si>
   <si>
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
@@ -2099,7 +2301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP88"/>
+  <dimension ref="A1:AP114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.6875" customWidth="true" bestFit="true"/>
@@ -6142,35 +6344,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>344</v>
+        <v>218</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6218,7 +6416,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>343</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6227,47 +6425,47 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>221</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6279,15 +6477,17 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6324,31 +6524,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6371,21 +6571,23 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6397,17 +6599,15 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>347</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>140</v>
+        <v>336</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6444,16 +6644,16 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>227</v>
@@ -6480,7 +6680,7 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6491,10 +6691,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6505,7 +6705,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6514,23 +6714,19 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6578,19 +6774,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6599,10 +6795,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6613,10 +6809,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6624,10 +6820,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6639,13 +6835,13 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6684,31 +6880,31 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6720,7 +6916,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6731,21 +6927,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6760,14 +6958,12 @@
         <v>139</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>140</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6804,16 +7000,16 @@
         <v>82</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>227</v>
@@ -6840,7 +7036,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6854,11 +7050,9 @@
         <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C40" t="s" s="2">
         <v>359</v>
       </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6879,13 +7073,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>360</v>
+        <v>217</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>218</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>219</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6936,19 +7130,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6960,7 +7154,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6971,10 +7165,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6985,7 +7179,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6997,13 +7191,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7042,31 +7236,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7078,7 +7272,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7089,10 +7283,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7100,10 +7294,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>367</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7115,22 +7309,24 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7160,31 +7356,31 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>227</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7196,7 +7392,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7207,20 +7403,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="B43" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>370</v>
-      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7235,13 +7429,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7250,7 +7444,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7268,13 +7462,11 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7292,19 +7484,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7316,7 +7508,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7327,12 +7519,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7353,13 +7547,13 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>218</v>
+        <v>377</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7410,19 +7604,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7434,7 +7628,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7445,10 +7639,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7459,7 +7653,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7471,13 +7665,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>219</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7516,31 +7710,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7552,7 +7746,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7563,10 +7757,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7574,10 +7768,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7589,24 +7783,22 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7636,31 +7828,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>227</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7672,7 +7864,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7683,10 +7875,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7694,7 +7886,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7709,25 +7901,27 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>82</v>
@@ -7766,10 +7960,10 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
@@ -7778,7 +7972,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7801,20 +7995,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -7829,13 +8021,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7886,19 +8078,19 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7910,7 +8102,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7921,18 +8113,20 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -7947,13 +8141,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8004,19 +8198,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8028,7 +8222,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8039,10 +8233,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8053,7 +8247,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8065,13 +8259,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>219</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8110,31 +8304,31 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8146,7 +8340,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8157,10 +8351,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8168,10 +8362,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8183,24 +8377,22 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8230,31 +8422,31 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8266,7 +8458,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8277,10 +8469,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8288,7 +8480,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8303,22 +8495,24 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8360,10 +8554,10 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>93</v>
@@ -8372,7 +8566,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8395,10 +8589,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8406,7 +8600,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
@@ -8421,24 +8615,22 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>82</v>
@@ -8480,10 +8672,10 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>93</v>
@@ -8492,7 +8684,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8515,10 +8707,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8526,10 +8718,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8541,22 +8733,24 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>397</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -8598,10 +8792,10 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>93</v>
@@ -8610,7 +8804,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8633,10 +8827,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8647,7 +8841,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8656,23 +8850,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>394</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8720,7 +8910,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>245</v>
+        <v>374</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8741,10 +8931,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8755,10 +8945,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8784,13 +8974,13 @@
         <v>217</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>249</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>250</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>251</v>
+        <v>398</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8840,7 +9030,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>252</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8849,7 +9039,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -8861,10 +9051,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8875,10 +9065,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8901,18 +9091,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>256</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8936,13 +9126,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8960,7 +9150,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>260</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8981,10 +9171,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8995,10 +9185,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9021,18 +9211,18 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9080,7 +9270,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>268</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9101,10 +9291,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>270</v>
+        <v>414</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9115,10 +9305,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9141,20 +9331,18 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>273</v>
+        <v>416</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>274</v>
+        <v>417</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9202,7 +9390,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>277</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9223,10 +9411,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9237,10 +9425,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9248,13 +9436,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9263,19 +9451,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>282</v>
+        <v>422</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>283</v>
+        <v>423</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>284</v>
+        <v>424</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9324,7 +9512,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>285</v>
+        <v>420</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9333,7 +9521,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9342,27 +9530,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>286</v>
+        <v>427</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>287</v>
+        <v>428</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9385,20 +9573,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>405</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9422,13 +9606,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9446,7 +9630,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>220</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9455,10 +9639,10 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9467,10 +9651,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>413</v>
+        <v>221</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9481,24 +9665,24 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>415</v>
+        <v>138</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
@@ -9507,20 +9691,18 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>140</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>223</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9544,29 +9726,31 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>227</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9578,33 +9762,33 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>423</v>
+        <v>221</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9618,28 +9802,28 @@
         <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>426</v>
+        <v>229</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>427</v>
+        <v>230</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>428</v>
+        <v>231</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>429</v>
+        <v>232</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>430</v>
+        <v>233</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9688,7 +9872,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>425</v>
+        <v>234</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9709,10 +9893,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>431</v>
+        <v>235</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>432</v>
+        <v>236</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9749,17 +9933,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9784,13 +9966,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9808,7 +9990,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>433</v>
+        <v>220</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9820,47 +10002,47 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>441</v>
+        <v>221</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
@@ -9869,20 +10051,18 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>444</v>
+        <v>140</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9906,41 +10086,43 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>443</v>
+        <v>227</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -9949,10 +10131,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>450</v>
+        <v>221</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9963,12 +10145,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
       </c>
@@ -9989,17 +10173,15 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10048,45 +10230,45 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>451</v>
+        <v>227</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10109,17 +10291,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>461</v>
+        <v>217</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>218</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10168,7 +10348,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>460</v>
+        <v>220</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10180,33 +10360,33 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>467</v>
+        <v>221</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10214,7 +10394,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>81</v>
@@ -10229,20 +10409,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>470</v>
+        <v>139</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>471</v>
+        <v>354</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10278,19 +10454,19 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>469</v>
+        <v>227</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10302,7 +10478,7 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>475</v>
+        <v>144</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10311,10 +10487,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10325,18 +10501,20 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>93</v>
@@ -10351,13 +10529,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10408,19 +10586,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10432,7 +10610,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10443,21 +10621,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10469,17 +10647,15 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10528,19 +10704,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10563,46 +10739,42 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>447</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>482</v>
+        <v>354</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10638,19 +10810,19 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>484</v>
+        <v>227</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10674,7 +10846,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10685,10 +10857,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10696,7 +10868,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>93</v>
@@ -10711,22 +10883,24 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>486</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>487</v>
+        <v>364</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>82</v>
@@ -10768,19 +10942,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>485</v>
+        <v>367</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10789,10 +10963,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>491</v>
+        <v>136</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10803,10 +10977,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
+        <v>452</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10829,13 +11003,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>486</v>
+        <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>493</v>
+        <v>370</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>494</v>
+        <v>371</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10847,7 +11021,7 @@
         <v>82</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>82</v>
@@ -10886,7 +11060,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>492</v>
+        <v>374</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10895,7 +11069,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -10907,10 +11081,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>495</v>
+        <v>136</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -10921,18 +11095,20 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>93</v>
@@ -10947,20 +11123,16 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>497</v>
+        <v>354</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -10984,13 +11156,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11008,31 +11180,31 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>496</v>
+        <v>227</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11043,10 +11215,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>505</v>
+        <v>455</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>505</v>
+        <v>446</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11057,7 +11229,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11069,20 +11241,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11106,13 +11274,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11130,31 +11298,31 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>505</v>
+        <v>220</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>423</v>
+        <v>221</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11165,10 +11333,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>512</v>
+        <v>456</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>512</v>
+        <v>448</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11179,7 +11347,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11191,18 +11359,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>513</v>
+        <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>514</v>
+        <v>354</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>515</v>
+        <v>355</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>516</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11238,31 +11404,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>512</v>
+        <v>227</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11274,7 +11440,7 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11285,10 +11451,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>518</v>
+        <v>457</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>518</v>
+        <v>450</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11296,7 +11462,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>93</v>
@@ -11311,22 +11477,24 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>519</v>
+        <v>364</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>82</v>
@@ -11368,10 +11536,10 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>518</v>
+        <v>367</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>93</v>
@@ -11380,7 +11548,7 @@
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11389,10 +11557,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>521</v>
+        <v>136</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11571,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>458</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11417,7 +11585,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11426,20 +11594,18 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>523</v>
+        <v>192</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>524</v>
+        <v>370</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11488,13 +11654,13 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>522</v>
+        <v>374</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -11509,10 +11675,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>528</v>
+        <v>136</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11523,10 +11689,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>529</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11534,10 +11700,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11546,19 +11712,19 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>530</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>532</v>
+        <v>365</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>533</v>
+        <v>366</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11566,7 +11732,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>82</v>
@@ -11608,19 +11774,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>529</v>
+        <v>367</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11629,10 +11795,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>534</v>
+        <v>136</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11643,10 +11809,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>535</v>
+        <v>462</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>463</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11657,7 +11823,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11666,23 +11832,19 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>470</v>
+        <v>394</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>536</v>
+        <v>370</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11730,13 +11892,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>535</v>
+        <v>374</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -11751,10 +11913,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>541</v>
+        <v>136</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11765,10 +11927,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>542</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>542</v>
+        <v>464</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11788,19 +11950,23 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11848,7 +12014,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11860,7 +12026,7 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11869,10 +12035,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -11883,21 +12049,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>543</v>
+        <v>465</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>465</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -11906,19 +12072,19 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>139</v>
+        <v>217</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>140</v>
+        <v>249</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>142</v>
+        <v>251</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11968,19 +12134,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -11989,10 +12155,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12003,45 +12169,43 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>466</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>544</v>
+        <v>466</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>482</v>
+        <v>256</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12090,19 +12254,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>484</v>
+        <v>260</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12111,10 +12275,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12125,10 +12289,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>467</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>467</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12136,7 +12300,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>93</v>
@@ -12151,19 +12315,17 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>546</v>
+        <v>264</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12188,13 +12350,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12212,10 +12374,10 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>268</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>93</v>
@@ -12230,16 +12392,16 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -12247,10 +12409,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>550</v>
+        <v>468</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>550</v>
+        <v>468</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12273,19 +12435,19 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>551</v>
+        <v>272</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>552</v>
+        <v>273</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>345</v>
+        <v>274</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>553</v>
+        <v>275</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>347</v>
+        <v>276</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12334,7 +12496,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>550</v>
+        <v>277</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12352,27 +12514,27 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>350</v>
+        <v>278</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>469</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>469</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12392,22 +12554,22 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>556</v>
+        <v>281</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>557</v>
+        <v>282</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>558</v>
+        <v>283</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>408</v>
+        <v>284</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12432,13 +12594,13 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
@@ -12456,7 +12618,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>555</v>
+        <v>285</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12465,7 +12627,7 @@
         <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12477,10 +12639,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>136</v>
+        <v>286</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>413</v>
+        <v>287</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12491,21 +12653,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>559</v>
+        <v>470</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>559</v>
+        <v>470</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12520,16 +12682,16 @@
         <v>192</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>560</v>
+        <v>471</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>419</v>
+        <v>474</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12554,13 +12716,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>561</v>
+        <v>475</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12578,16 +12740,16 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>559</v>
+        <v>470</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>105</v>
@@ -12596,41 +12758,41 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>422</v>
+        <v>136</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>479</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>563</v>
+        <v>479</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>82</v>
@@ -12639,19 +12801,19 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>564</v>
+        <v>481</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>565</v>
+        <v>482</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12676,13 +12838,11 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12700,7 +12860,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>563</v>
+        <v>479</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12718,23 +12878,3157 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y91" s="2"/>
+      <c r="Z91" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AN88" t="s" s="2">
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI112" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP88" t="s" s="2">
+      <c r="AJ112" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP88">
+  <autoFilter ref="A1:AP114">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12744,7 +16038,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
